--- a/stores/Resultados_random_forest.xlsx
+++ b/stores/Resultados_random_forest.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\Academia\Maestría MEcA\Big data y machine learning\Taller 2\ProblemSet2_G10\stores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7E8042-718B-4657-85DB-163EBBEE3B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50601F16-1E6E-4449-A56B-DE1267759AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{6A558E66-D680-4CA7-BD82-ADD54E8BFE60}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="random_forest" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
   <si>
     <t>Prueba</t>
   </si>
@@ -50,9 +51,6 @@
     <t>min.node.size</t>
   </si>
   <si>
-    <t>RF con train</t>
-  </si>
-  <si>
     <t>AUC  validation</t>
   </si>
   <si>
@@ -62,9 +60,6 @@
     <t>No Pobre</t>
   </si>
   <si>
-    <t>0.9371</t>
-  </si>
-  <si>
     <t>F1</t>
   </si>
   <si>
@@ -75,13 +70,22 @@
   </si>
   <si>
     <t>Prediction</t>
+  </si>
+  <si>
+    <t>RF con train sin interacción hacinamiento y n_personas</t>
+  </si>
+  <si>
+    <t>RF con train con interacción hacinamiento</t>
+  </si>
+  <si>
+    <t>RF con train_raw sin interacción hacinamiento y n_personas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,13 +93,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -110,13 +128,64 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -446,103 +515,762 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC97EA62-D54D-41EF-83DD-100D37B8F67B}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17.1328125" customWidth="1"/>
+    <col min="1" max="1" width="44.59765625" customWidth="1"/>
     <col min="4" max="4" width="11.796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="J1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2000</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.93710000000000004</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
+        <v>19580</v>
+      </c>
+      <c r="H3" s="5">
+        <v>46588</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="K3" s="6">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="L3" s="6">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="6">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>32465</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3630</v>
+      </c>
+      <c r="M4" s="5">
+        <f>L4+K5</f>
+        <v>10745</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="6">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>7115</v>
+      </c>
+      <c r="L5" s="5">
+        <v>35950</v>
+      </c>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>500</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0.93801999999999996</v>
+      </c>
+      <c r="F7">
+        <v>0.871</v>
+      </c>
+      <c r="G7">
+        <v>19421</v>
+      </c>
+      <c r="H7">
+        <v>46747</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>32539</v>
+      </c>
+      <c r="L7">
+        <v>3612</v>
+      </c>
+      <c r="M7">
+        <f>L7+K8</f>
+        <v>10653</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>7041</v>
+      </c>
+      <c r="L8">
+        <v>35968</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C10" s="5">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.93818000000000001</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.87139999999999995</v>
+      </c>
+      <c r="G10" s="5">
+        <v>19414</v>
+      </c>
+      <c r="H10" s="5">
+        <v>46754</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>32549</v>
+      </c>
+      <c r="L10" s="5">
+        <v>3594</v>
+      </c>
+      <c r="M10" s="5">
+        <f>L10+K11</f>
+        <v>10625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="6">
+        <v>1</v>
+      </c>
+      <c r="K11" s="5">
+        <v>7031</v>
+      </c>
+      <c r="L11" s="5">
+        <v>35986</v>
+      </c>
+      <c r="M11" s="5"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C13" s="5">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E13" s="5">
+        <v>0.93613000000000002</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.86909999999999998</v>
+      </c>
+      <c r="G13" s="5">
+        <v>19421</v>
+      </c>
+      <c r="H13" s="5">
+        <v>46747</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" s="6">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>32554</v>
+      </c>
+      <c r="L13" s="5">
+        <v>3766</v>
+      </c>
+      <c r="M13" s="5">
+        <f>L13+K14</f>
+        <v>10792</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="6">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5">
+        <v>7026</v>
+      </c>
+      <c r="L14" s="5">
+        <v>35814</v>
+      </c>
+      <c r="M14" s="5"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C16" s="5">
         <v>6</v>
       </c>
-      <c r="H2" t="s">
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0.94569999999999999</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0.8841</v>
+      </c>
+      <c r="G16" s="5">
+        <v>18406</v>
+      </c>
+      <c r="H16" s="5">
+        <v>47762</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="6">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>32763</v>
+      </c>
+      <c r="L16" s="5">
+        <v>2821</v>
+      </c>
+      <c r="M16" s="5">
+        <f>L16+K17</f>
+        <v>9638</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="6">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5">
+        <v>6817</v>
+      </c>
+      <c r="L17" s="5">
+        <v>36759</v>
+      </c>
+      <c r="M17" s="5"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C19" s="5">
+        <v>8</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.9456</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0.88519999999999999</v>
+      </c>
+      <c r="G19" s="5">
+        <v>18314</v>
+      </c>
+      <c r="H19" s="5">
+        <v>47854</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="6">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>32673</v>
+      </c>
+      <c r="L19" s="5">
+        <v>2668</v>
+      </c>
+      <c r="M19" s="5">
+        <f>L19+K20</f>
+        <v>9575</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="6">
+        <v>1</v>
+      </c>
+      <c r="K20" s="5">
+        <v>6907</v>
+      </c>
+      <c r="L20" s="5">
+        <v>36912</v>
+      </c>
+      <c r="M20" s="5"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>1000</v>
+      </c>
+      <c r="C22">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>0.94404999999999994</v>
+      </c>
+      <c r="F22">
+        <v>0.88460000000000005</v>
+      </c>
+      <c r="G22">
+        <v>18368</v>
+      </c>
+      <c r="H22">
+        <v>47800</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>32611</v>
+      </c>
+      <c r="L22">
+        <v>2661</v>
+      </c>
+      <c r="M22">
+        <f>L22+K23</f>
+        <v>9630</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>6969</v>
+      </c>
+      <c r="L23">
+        <v>36919</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A25" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="5">
+        <v>2000</v>
+      </c>
+      <c r="C25" s="5">
         <v>7</v>
       </c>
-      <c r="K2" t="s">
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0.94598000000000004</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0.8851</v>
+      </c>
+      <c r="G25" s="5">
+        <v>18368</v>
+      </c>
+      <c r="H25" s="5">
+        <v>47800</v>
+      </c>
+      <c r="I25" s="5"/>
+      <c r="J25" s="6">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5">
+        <v>32698</v>
+      </c>
+      <c r="L25" s="5">
+        <v>2697</v>
+      </c>
+      <c r="M25" s="5">
+        <f>L25+K26</f>
+        <v>9579</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="6">
+        <v>1</v>
+      </c>
+      <c r="K26" s="5">
+        <v>6882</v>
+      </c>
+      <c r="L26" s="5">
+        <v>36883</v>
+      </c>
+      <c r="M26" s="5"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A28" s="8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
+      <c r="B28" s="9">
         <v>2000</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C28" s="9">
         <v>8</v>
       </c>
-      <c r="G3">
-        <v>19580</v>
-      </c>
-      <c r="H3">
-        <v>46588</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3">
+      <c r="D28" s="9">
+        <v>1</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.94562999999999997</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0.88490000000000002</v>
+      </c>
+      <c r="G28" s="9">
+        <v>18310</v>
+      </c>
+      <c r="H28" s="9">
+        <v>47858</v>
+      </c>
+      <c r="I28" s="9"/>
+      <c r="J28" s="10">
         <v>0</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="J4">
+      <c r="K28">
+        <v>32679</v>
+      </c>
+      <c r="L28">
+        <v>2693</v>
+      </c>
+      <c r="M28">
+        <f>L28+K29</f>
+        <v>9594</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="10">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>6901</v>
+      </c>
+      <c r="L29">
+        <v>36887</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="9">
+        <v>2000</v>
+      </c>
+      <c r="C31" s="9">
+        <v>8</v>
+      </c>
+      <c r="D31" s="9">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>0.98307999999999995</v>
+      </c>
+      <c r="F31">
+        <v>0.94830000000000003</v>
+      </c>
+      <c r="G31">
+        <v>16955</v>
+      </c>
+      <c r="H31">
+        <v>49213</v>
+      </c>
+      <c r="J31" s="10">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>32465</v>
-      </c>
-      <c r="L4">
-        <v>3630</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>7115</v>
-      </c>
-      <c r="L5">
-        <v>35950</v>
+      <c r="K31">
+        <v>36702</v>
+      </c>
+      <c r="L31">
+        <v>1295</v>
+      </c>
+      <c r="M31">
+        <f>L31+K32</f>
+        <v>4173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J32" s="10">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>2878</v>
+      </c>
+      <c r="L32">
+        <v>38285</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34">
+        <v>1000</v>
+      </c>
+      <c r="C34">
+        <v>8</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>0.84723000000000004</v>
+      </c>
+      <c r="F34">
+        <v>0.54910000000000003</v>
+      </c>
+      <c r="G34">
+        <v>11638</v>
+      </c>
+      <c r="H34">
+        <v>54530</v>
+      </c>
+      <c r="J34" s="10">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>36166</v>
+      </c>
+      <c r="L34">
+        <v>4865</v>
+      </c>
+      <c r="M34">
+        <f>L34+K35</f>
+        <v>8279</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="J35" s="10">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>3414</v>
+      </c>
+      <c r="L35">
+        <v>5042</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37">
+        <v>0.97436</v>
+      </c>
+      <c r="F37">
+        <v>0.87370000000000003</v>
+      </c>
+      <c r="G37">
+        <v>11474</v>
+      </c>
+      <c r="H37">
+        <v>54694</v>
+      </c>
+      <c r="K37">
+        <v>38986</v>
+      </c>
+      <c r="L37">
+        <v>1761</v>
+      </c>
+      <c r="M37">
+        <f>L37+K38</f>
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="K38">
+        <v>594</v>
+      </c>
+      <c r="L38">
+        <v>8146</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="M4:M80">
+    <cfRule type="top10" dxfId="2" priority="5" bottom="1" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E28">
+    <cfRule type="top10" dxfId="1" priority="2" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F28">
+    <cfRule type="top10" dxfId="0" priority="1" rank="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41099052-3C6C-4AAA-AE22-53B474D1D399}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/stores/Resultados_random_forest.xlsx
+++ b/stores/Resultados_random_forest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\Academia\Maestría MEcA\Big data y machine learning\Taller 2\ProblemSet2_G10\stores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50601F16-1E6E-4449-A56B-DE1267759AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04763B50-204D-4449-8AA2-7AB7FB2CF630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{6A558E66-D680-4CA7-BD82-ADD54E8BFE60}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t>Prueba</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>RF con train_raw sin interacción hacinamiento y n_personas</t>
+  </si>
+  <si>
+    <t>Modelo con mejor puntaje</t>
   </si>
 </sst>
 </file>
@@ -102,7 +105,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -112,6 +115,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -145,16 +154,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -172,16 +191,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -515,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC97EA62-D54D-41EF-83DD-100D37B8F67B}">
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="44.59765625" customWidth="1"/>
@@ -523,7 +532,7 @@
     <col min="5" max="5" width="12.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -538,7 +547,7 @@
       </c>
       <c r="K1" s="3"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -569,7 +578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -604,7 +613,7 @@
       </c>
       <c r="M3" s="5"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -628,7 +637,7 @@
         <v>10745</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -649,60 +658,74 @@
       </c>
       <c r="M5" s="5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="9">
         <v>500</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="9">
         <v>4</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
+      <c r="D7" s="9">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9">
         <v>0.93801999999999996</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="9">
         <v>0.871</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="9">
         <v>19421</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="9">
         <v>46747</v>
       </c>
-      <c r="J7" s="1">
+      <c r="I7" s="9"/>
+      <c r="J7" s="10">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="9">
         <v>32539</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="9">
         <v>3612</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="9">
         <f>L7+K8</f>
         <v>10653</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
-      <c r="K8">
+      <c r="N7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="10">
+        <v>1</v>
+      </c>
+      <c r="K8" s="9">
         <v>7041</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="9">
         <v>35968</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="M8" s="9"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
@@ -742,7 +765,7 @@
         <v>10625</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -763,7 +786,7 @@
       </c>
       <c r="M11" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
         <v>11</v>
       </c>
@@ -803,7 +826,7 @@
         <v>10792</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -824,7 +847,7 @@
       </c>
       <c r="M14" s="5"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
         <v>11</v>
       </c>
@@ -1058,32 +1081,31 @@
       <c r="M26" s="5"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28">
         <v>2000</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28">
         <v>8</v>
       </c>
-      <c r="D28" s="9">
-        <v>1</v>
-      </c>
-      <c r="E28" s="9">
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
         <v>0.94562999999999997</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28">
         <v>0.88490000000000002</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28">
         <v>18310</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28">
         <v>47858</v>
       </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="10">
+      <c r="J28" s="1">
         <v>0</v>
       </c>
       <c r="K28">
@@ -1098,16 +1120,7 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="10">
+      <c r="J29" s="1">
         <v>1</v>
       </c>
       <c r="K29">
@@ -1118,16 +1131,16 @@
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31">
         <v>2000</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31">
         <v>8</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
@@ -1142,7 +1155,7 @@
       <c r="H31">
         <v>49213</v>
       </c>
-      <c r="J31" s="10">
+      <c r="J31" s="1">
         <v>0</v>
       </c>
       <c r="K31">
@@ -1157,7 +1170,7 @@
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="J32" s="10">
+      <c r="J32" s="1">
         <v>1</v>
       </c>
       <c r="K32">
@@ -1168,7 +1181,7 @@
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B34">
@@ -1192,7 +1205,7 @@
       <c r="H34">
         <v>54530</v>
       </c>
-      <c r="J34" s="10">
+      <c r="J34" s="1">
         <v>0</v>
       </c>
       <c r="K34">
@@ -1207,7 +1220,7 @@
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="J35" s="10">
+      <c r="J35" s="1">
         <v>1</v>
       </c>
       <c r="K35">
@@ -1218,7 +1231,7 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E37">
@@ -1253,14 +1266,14 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M4:M80">
-    <cfRule type="top10" dxfId="2" priority="5" bottom="1" rank="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E3:E28">
-    <cfRule type="top10" dxfId="1" priority="2" rank="1"/>
+    <cfRule type="top10" dxfId="2" priority="2" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F28">
-    <cfRule type="top10" dxfId="0" priority="1" rank="1"/>
+    <cfRule type="top10" dxfId="1" priority="1" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:M80">
+    <cfRule type="top10" dxfId="0" priority="5" bottom="1" rank="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
